--- a/samples/golden/cm01_journal_golden.xlsx
+++ b/samples/golden/cm01_journal_golden.xlsx
@@ -23378,7 +23378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -23594,6 +23594,20 @@
       </c>
       <c r="B20" s="151" t="n">
         <v>469861</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="211" t="inlineStr">
+        <is>
+          <t>EVIDENCE FILES</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="151" t="inlineStr">
+        <is>
+          <t>(none attached)</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -23607,7 +23621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -23815,6 +23829,20 @@
         <v>150000</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="211" t="inlineStr">
+        <is>
+          <t>EVIDENCE FILES</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="151" t="inlineStr">
+        <is>
+          <t>(none attached)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/samples/golden/cm01_journal_golden.xlsx
+++ b/samples/golden/cm01_journal_golden.xlsx
@@ -2675,7 +2675,7 @@
       </c>
       <c r="H10" s="150" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANUAL RECIEPT </t>
+          <t>SHORT PAYMENT</t>
         </is>
       </c>
       <c r="I10" s="151" t="n"/>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="H11" s="155" t="inlineStr">
         <is>
-          <t xml:space="preserve">MANUAL RECIEPT </t>
+          <t>SHORT PAYMENT</t>
         </is>
       </c>
       <c r="I11" s="151" t="n"/>
@@ -2778,7 +2778,7 @@
       <c r="M11" s="151" t="n"/>
       <c r="N11" s="210" t="inlineStr">
         <is>
-          <t>payment difference on payment reference DEP-9999-UBA</t>
+          <t>DEP-4471-BICEC</t>
         </is>
       </c>
       <c r="O11" s="151" t="n"/>
